--- a/resume_screening_results.xlsx
+++ b/resume_screening_results.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screening Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Screening Results'!$A$1:$K$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Screening Results'!$A$1:$K$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -687,17 +687,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>neha jacob</t>
+          <t>BPO_13964744</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>59.63</v>
+        <v>36.92</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>46.14</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46.15</v>
+        <v>15.38</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -711,18 +711,20 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>communication, machine learning, python, pytorch, sql, tensorflow</t>
+          <t>communication, sql</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, deep learning, docker, gcp, kubernetes, nlp</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n"/>
+          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, tensorflow</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Bachelors</t>
+          <t>Masters, High School</t>
         </is>
       </c>
     </row>
@@ -732,14 +734,14 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>neha_kumar</t>
+          <t>INFORMATION-TECHNOLOGY_10089434</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>37.25</v>
+        <v>35.38</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46.62</v>
+        <v>43.95</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>15.38</v>
@@ -756,18 +758,18 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>communication, python</t>
+          <t>azure, sql</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, pytorch, sql, tensorflow</t>
+          <t>aws, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, tensorflow</t>
         </is>
       </c>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Bachelors</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -777,14 +779,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>BPO_13964744</t>
+          <t>INFORMATION-TECHNOLOGY_10247517</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>36.92</v>
+        <v>33.58</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46.14</v>
+        <v>41.38</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>15.38</v>
@@ -809,12 +811,10 @@
           <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, tensorflow</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Masters, High School</t>
+          <t>Masters</t>
         </is>
       </c>
     </row>
@@ -824,17 +824,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>INFORMATION-TECHNOLOGY_10089434</t>
+          <t>sam</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>35.38</v>
+        <v>32.88</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>43.95</v>
+        <v>43.68</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>15.38</v>
+        <v>7.69</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -848,18 +848,18 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>azure, sql</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>aws, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, tensorflow</t>
+          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, tensorflow</t>
         </is>
       </c>
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bachelors</t>
         </is>
       </c>
     </row>
@@ -869,17 +869,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INFORMATION-TECHNOLOGY_10247517</t>
+          <t>AlthafMohammadBabu_Resume</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>33.58</v>
+        <v>32.66</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>41.38</v>
+        <v>43.36</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>15.38</v>
+        <v>7.69</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -893,18 +893,18 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>communication, sql</t>
+          <t>python</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, tensorflow</t>
+          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, pytorch, sql, tensorflow</t>
         </is>
       </c>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -914,14 +914,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sam</t>
+          <t>althaf</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>32.88</v>
+        <v>32.66</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>43.68</v>
+        <v>43.36</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>7.69</v>
@@ -938,18 +938,18 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>python</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, tensorflow</t>
+          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, pytorch, sql, tensorflow</t>
         </is>
       </c>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Bachelors</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -959,14 +959,14 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>AlthafMohammadBabu_Resume</t>
+          <t>AVIATION_10176815</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>32.66</v>
+        <v>32.02</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>43.36</v>
+        <v>42.44</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>7.69</v>
@@ -983,18 +983,18 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, pytorch, sql, tensorflow</t>
+          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bachelors</t>
         </is>
       </c>
     </row>
@@ -1004,14 +1004,14 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>althaf</t>
+          <t>BUSINESS-DEVELOPMENT_10235211</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>32.66</v>
+        <v>30.31</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>43.36</v>
+        <v>40.01</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>7.69</v>
@@ -1028,18 +1028,18 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, pytorch, sql, tensorflow</t>
+          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bachelors, Associate, High School</t>
         </is>
       </c>
     </row>
@@ -1049,14 +1049,14 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>AVIATION_10176815</t>
+          <t>APPAREL_10562768</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>32.02</v>
+        <v>30.22</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>42.44</v>
+        <v>39.87</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7.69</v>
@@ -1084,7 +1084,7 @@
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Bachelors</t>
+          <t>Masters</t>
         </is>
       </c>
     </row>
@@ -1094,14 +1094,14 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BUSINESS-DEVELOPMENT_10235211</t>
+          <t>AVIATION_10189110</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>30.31</v>
+        <v>29.62</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>40.01</v>
+        <v>39.02</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>7.69</v>
@@ -1126,10 +1126,12 @@
           <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n"/>
+      <c r="J15" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Bachelors, Associate, High School</t>
+          <t>Masters, Bachelors, High School</t>
         </is>
       </c>
     </row>
@@ -1139,14 +1141,14 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>APPAREL_10562768</t>
+          <t>wikki</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>30.22</v>
+        <v>28.67</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>39.87</v>
+        <v>37.66</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>7.69</v>
@@ -1163,12 +1165,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, tensorflow</t>
         </is>
       </c>
       <c r="J16" s="2" t="n"/>
@@ -1184,17 +1186,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>AVIATION_10189110</t>
+          <t>CONSTRUCTION_10041713</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>29.62</v>
+        <v>28.45</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>39.02</v>
+        <v>34.04</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>7.69</v>
+        <v>15.38</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1208,20 +1210,20 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>communication, sql</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, tensorflow</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Masters, Bachelors, High School</t>
+          <t>Masters</t>
         </is>
       </c>
     </row>
@@ -1231,17 +1233,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>wikki</t>
+          <t>ENGINEERING_10030015</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>28.67</v>
+        <v>27.09</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>37.66</v>
+        <v>38.7</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>7.69</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1255,18 +1257,18 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, tensorflow</t>
+          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1276,17 +1278,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CONSTRUCTION_10041713</t>
+          <t>HR_10399912</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>28.45</v>
+        <v>26.79</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>34.04</v>
+        <v>38.27</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>15.38</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1300,20 +1302,20 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>communication, sql</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, tensorflow</t>
+          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Masters, Bachelors, High School</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1325,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ENGINEERING_10030015</t>
+          <t>ENGINEERING_10219099</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>27.09</v>
+        <v>26.54</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>38.7</v>
+        <v>34.62</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1347,18 +1349,20 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n"/>
+          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bachelors, High School</t>
         </is>
       </c>
     </row>
@@ -1368,17 +1372,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>HR_10399912</t>
+          <t>BANKING_10329506</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>26.79</v>
+        <v>26.47</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>38.27</v>
+        <v>34.52</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1392,20 +1396,18 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>8</v>
-      </c>
+          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Masters, Bachelors, High School</t>
+          <t>Bachelors</t>
         </is>
       </c>
     </row>
@@ -1415,14 +1417,14 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ENGINEERING_10219099</t>
+          <t>sinu</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>26.54</v>
+        <v>24.8</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>34.62</v>
+        <v>32.14</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>7.69</v>
@@ -1447,12 +1449,10 @@
           <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
-      <c r="J22" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Bachelors, High School</t>
+          <t>Masters, Bachelors</t>
         </is>
       </c>
     </row>
@@ -1462,14 +1462,14 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>BANKING_10329506</t>
+          <t>FINANCE_10549585</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>26.47</v>
+        <v>24.6</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>34.52</v>
+        <v>31.85</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>7.69</v>
@@ -1497,7 +1497,7 @@
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Bachelors</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1507,17 +1507,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>sinu</t>
+          <t>BANKING_10909673</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>24.8</v>
+        <v>24.51</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>32.14</v>
+        <v>35.01</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>7.69</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1531,18 +1531,18 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Masters, Bachelors</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1552,14 +1552,14 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FINANCE_10549585</t>
+          <t>ADVOCATE_10344379</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>24.6</v>
+        <v>24.31</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>31.85</v>
+        <v>31.43</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>7.69</v>
@@ -1587,7 +1587,7 @@
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1597,14 +1597,14 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>BANKING_10909673</t>
+          <t>CONSULTANT_10984392</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>24.51</v>
+        <v>23.91</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>35.01</v>
+        <v>34.16</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>0</v>
@@ -1632,7 +1632,7 @@
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bachelors</t>
         </is>
       </c>
     </row>
@@ -1642,14 +1642,14 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ADVOCATE_10344379</t>
+          <t>susan</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>24.31</v>
+        <v>23.61</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>31.43</v>
+        <v>30.43</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>7.69</v>
@@ -1677,7 +1677,7 @@
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>High School</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1687,17 +1687,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CONSULTANT_10984392</t>
+          <t>FINANCE_11441764</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>23.91</v>
+        <v>23.55</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>34.16</v>
+        <v>30.35</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1711,18 +1711,18 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, tensorflow</t>
         </is>
       </c>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Bachelors</t>
+          <t>Masters, Bachelors</t>
         </is>
       </c>
     </row>
@@ -1732,14 +1732,14 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>susan</t>
+          <t>shifa</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>23.61</v>
+        <v>23.5</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>30.43</v>
+        <v>30.28</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>7.69</v>
@@ -1767,7 +1767,7 @@
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Masters</t>
         </is>
       </c>
     </row>
@@ -1777,14 +1777,14 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FINANCE_11441764</t>
+          <t>DIGITAL-MEDIA_10515955</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>23.55</v>
+        <v>23.49</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>30.35</v>
+        <v>30.26</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>7.69</v>
@@ -1801,18 +1801,20 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, tensorflow</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="n"/>
+          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Masters, Bachelors</t>
+          <t>Bachelors</t>
         </is>
       </c>
     </row>
@@ -1822,14 +1824,14 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>shifa</t>
+          <t>BPO_11183737</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>23.5</v>
+        <v>23.38</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>30.28</v>
+        <v>30.11</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>7.69</v>
@@ -1854,10 +1856,12 @@
           <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
-      <c r="J31" s="2" t="n"/>
+      <c r="J31" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1867,14 +1871,14 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>DIGITAL-MEDIA_10515955</t>
+          <t>CONSULTANT_10332998</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>23.49</v>
+        <v>23.25</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>30.26</v>
+        <v>29.92</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>7.69</v>
@@ -1899,12 +1903,10 @@
           <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
-      <c r="J32" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Bachelors</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1914,14 +1916,14 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>BPO_11183737</t>
+          <t>ARTS_10830646</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>23.38</v>
+        <v>23.13</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>30.11</v>
+        <v>29.74</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>7.69</v>
@@ -1947,11 +1949,11 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bachelors, High School</t>
         </is>
       </c>
     </row>
@@ -1961,17 +1963,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CONSULTANT_10332998</t>
+          <t>BUSINESS-DEVELOPMENT_10228751</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>23.25</v>
+        <v>23.02</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>29.92</v>
+        <v>32.88</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>7.69</v>
+        <v>0</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -1985,15 +1987,17 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="n"/>
+          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
           <t>None</t>
@@ -2006,14 +2010,14 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ARTS_10830646</t>
+          <t>AUTOMOBILE_11257723</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>23.13</v>
+        <v>22.88</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>29.74</v>
+        <v>29.39</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>7.69</v>
@@ -2038,12 +2042,10 @@
           <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
-      <c r="J35" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Bachelors, High School</t>
+          <t>Bachelors</t>
         </is>
       </c>
     </row>
@@ -2053,14 +2055,14 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>BUSINESS-DEVELOPMENT_10228751</t>
+          <t>ACCOUNTANT_11163645</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>23.02</v>
+        <v>22.84</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>32.88</v>
+        <v>32.62</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>0</v>
@@ -2085,9 +2087,7 @@
           <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
-      <c r="J36" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
           <t>None</t>
@@ -2100,14 +2100,14 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>AUTOMOBILE_11257723</t>
+          <t>ARTS_11187796</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>22.88</v>
+        <v>22.49</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>29.39</v>
+        <v>28.83</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>7.69</v>
@@ -2145,14 +2145,14 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNTANT_11163645</t>
+          <t>APPAREL_10182582</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>22.84</v>
+        <v>22.42</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>32.62</v>
+        <v>32.02</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>0</v>
@@ -2180,7 +2180,7 @@
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Masters</t>
         </is>
       </c>
     </row>
@@ -2190,17 +2190,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ARTS_11187796</t>
+          <t>DESIGNER_10748989</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>22.49</v>
+        <v>21.96</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>28.83</v>
+        <v>31.38</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>7.69</v>
+        <v>0</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2214,18 +2214,18 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Bachelors</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2235,14 +2235,14 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>APPAREL_10182582</t>
+          <t>PUBLIC-RELATIONS_10554045</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>22.42</v>
+        <v>21.27</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>32.02</v>
+        <v>30.38</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>0</v>
@@ -2270,7 +2270,7 @@
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Masters</t>
+          <t>Masters, Bachelors</t>
         </is>
       </c>
     </row>
@@ -2280,14 +2280,14 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>DESIGNER_10748989</t>
+          <t>TEACHER_10527994</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>21.96</v>
+        <v>21.24</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>31.38</v>
+        <v>30.34</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>0</v>
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC-RELATIONS_10554045</t>
+          <t>ADVOCATE_10659182</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>21.27</v>
+        <v>21.09</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>30.38</v>
+        <v>26.83</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2349,18 +2349,20 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="n"/>
+          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Masters, Bachelors</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2370,17 +2372,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>TEACHER_10527994</t>
+          <t>CONSTRUCTION_10100240</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>21.24</v>
+        <v>20.42</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>30.34</v>
+        <v>25.87</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2394,18 +2396,20 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="n"/>
+          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -2415,17 +2419,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ADVOCATE_10659182</t>
+          <t>ADVOCATE_10186968</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>21.09</v>
+        <v>19.82</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>26.83</v>
+        <v>28.32</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>7.69</v>
+        <v>0</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2439,20 +2443,18 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>10</v>
-      </c>
+          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bachelors, High School</t>
         </is>
       </c>
     </row>
@@ -2462,14 +2464,14 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CONSTRUCTION_10100240</t>
+          <t>SALES_10464113</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>20.42</v>
+        <v>19.14</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>25.87</v>
+        <v>24.05</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>7.69</v>
@@ -2495,11 +2497,11 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>High School</t>
+          <t>Bachelors, High School</t>
         </is>
       </c>
     </row>
@@ -2509,14 +2511,14 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ADVOCATE_10186968</t>
+          <t>SALES_10138632</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>19.82</v>
+        <v>18.45</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>28.32</v>
+        <v>26.35</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>0</v>
@@ -2554,17 +2556,17 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SALES_10464113</t>
+          <t>CHEF_10276858</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>19.14</v>
+        <v>17.99</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>24.05</v>
+        <v>25.7</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>7.69</v>
+        <v>0</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2578,16 +2580,16 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -2601,17 +2603,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SALES_10138632</t>
+          <t>CHEF_10001727</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>18.45</v>
+        <v>17.91</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>26.35</v>
+        <v>22.29</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2625,18 +2627,18 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Bachelors, High School</t>
+          <t>Masters, Bachelors</t>
         </is>
       </c>
     </row>
@@ -2646,14 +2648,14 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CHEF_10276858</t>
+          <t>FITNESS_10235429</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>17.99</v>
+        <v>17.82</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>25.7</v>
+        <v>25.46</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>0</v>
@@ -2678,12 +2680,10 @@
           <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
-      <c r="J49" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="J49" s="2" t="n"/>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Bachelors, High School</t>
+          <t>Masters, High School</t>
         </is>
       </c>
     </row>
@@ -2693,17 +2693,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CHEF_10001727</t>
+          <t>ACCOUNTANT_10554236</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>17.91</v>
+        <v>17.2</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>22.29</v>
+        <v>24.57</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>7.69</v>
+        <v>0</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -2717,18 +2717,18 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
       <c r="J50" s="2" t="n"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Masters, Bachelors</t>
+          <t>Bachelors</t>
         </is>
       </c>
     </row>
@@ -2738,14 +2738,14 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>FITNESS_10235429</t>
+          <t>HR_10694288</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>17.82</v>
+        <v>16.41</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>25.46</v>
+        <v>23.44</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>0</v>
@@ -2770,10 +2770,12 @@
           <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
-      <c r="J51" s="2" t="n"/>
+      <c r="J51" s="2" t="n">
+        <v>27</v>
+      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Masters, High School</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2783,17 +2785,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNTANT_10554236</t>
+          <t>PUBLIC-RELATIONS_10070224</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>17.2</v>
+        <v>15.77</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>24.57</v>
+        <v>19.23</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2807,18 +2809,20 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="n"/>
+          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>11</v>
+      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Bachelors</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2828,17 +2832,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>HR_10694288</t>
+          <t>AUTOMOBILE_11152490</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>16.41</v>
+        <v>15.49</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>23.44</v>
+        <v>18.83</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2852,20 +2856,18 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="n">
-        <v>27</v>
-      </c>
+          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n"/>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Masters, Bachelors, High School</t>
         </is>
       </c>
     </row>
@@ -2875,17 +2877,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC-RELATIONS_10070224</t>
+          <t>HEALTHCARE_10076271</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>15.77</v>
+        <v>14.79</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>19.23</v>
+        <v>21.13</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>7.69</v>
+        <v>0</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -2899,20 +2901,18 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>11</v>
-      </c>
+          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Masters, Bachelors</t>
         </is>
       </c>
     </row>
@@ -2922,14 +2922,14 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>AUTOMOBILE_11152490</t>
+          <t>AGRICULTURE_10953078</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>15.49</v>
+        <v>13.45</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>18.83</v>
+        <v>15.91</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>7.69</v>
@@ -2957,7 +2957,7 @@
       <c r="J55" s="2" t="n"/>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Masters, Bachelors, High School</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2967,14 +2967,14 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>HEALTHCARE_10076271</t>
+          <t>DESIGNER_10466583</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>14.79</v>
+        <v>13.17</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>21.13</v>
+        <v>18.82</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>0</v>
@@ -3002,7 +3002,7 @@
       <c r="J56" s="2" t="n"/>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Masters, Bachelors</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3012,17 +3012,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>AGRICULTURE_10953078</t>
+          <t>TEACHER_10504237</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>13.45</v>
+        <v>12.78</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>15.91</v>
+        <v>18.25</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>7.69</v>
+        <v>0</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3036,18 +3036,18 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
       <c r="J57" s="2" t="n"/>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bachelors</t>
         </is>
       </c>
     </row>
@@ -3057,14 +3057,14 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>DESIGNER_10466583</t>
+          <t>HEALTHCARE_10062724</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>13.17</v>
+        <v>11.84</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>18.82</v>
+        <v>16.92</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>0</v>
@@ -3089,7 +3089,9 @@
           <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
         </is>
       </c>
-      <c r="J58" s="2" t="n"/>
+      <c r="J58" s="2" t="n">
+        <v>18</v>
+      </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
           <t>None</t>
@@ -3102,14 +3104,14 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>TEACHER_10504237</t>
+          <t>ACCOUNTANT_10674770</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>12.78</v>
+        <v>11.39</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>18.25</v>
+        <v>16.28</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>0</v>
@@ -3137,7 +3139,7 @@
       <c r="J59" s="2" t="n"/>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Bachelors</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3147,17 +3149,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>HEALTHCARE_10062724</t>
+          <t>FITNESS_10268614</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>11.84</v>
+        <v>11.3</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>16.92</v>
+        <v>12.85</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3171,20 +3173,18 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>18</v>
-      </c>
+          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Masters</t>
         </is>
       </c>
     </row>
@@ -3194,14 +3194,14 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNTANT_10674770</t>
+          <t>DIGITAL-MEDIA_10005171</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>11.39</v>
+        <v>10.99</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>16.28</v>
+        <v>15.7</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>0</v>
@@ -3229,7 +3229,7 @@
       <c r="J61" s="2" t="n"/>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -3239,14 +3239,14 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>FITNESS_10268614</t>
+          <t>AGRICULTURE_11197262</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>11.3</v>
+        <v>4.65</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>12.85</v>
+        <v>3.35</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>7.69</v>
@@ -3278,98 +3278,8 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>DIGITAL-MEDIA_10005171</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="D63" s="2" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Low overall match with the job description.</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>aws, azure, communication, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="n"/>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>High School</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>AGRICULTURE_11197262</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>7.69</v>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Low overall match with the job description.</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>aws, azure, deep learning, docker, gcp, kubernetes, machine learning, nlp, python, pytorch, sql, tensorflow</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="n"/>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>Masters</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K64"/>
+  <autoFilter ref="A1:K62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>